--- a/artfynd/A 20942-2026 artfynd.xlsx
+++ b/artfynd/A 20942-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62155655</v>
+        <v>82883083</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>2563</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattstorp 7150/8150, Nrk</t>
+          <t>Ämtsätter, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514361.325022987</v>
+        <v>514222</v>
       </c>
       <c r="R2" t="n">
-        <v>6545056.026219307</v>
+        <v>6545162</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1960-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1960-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,21 +759,132 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Igenväxande fuktäng</t>
+          <t>Stråk med blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Rotben på klibbal, fuktig humus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>62155655</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mattstorp 7150/8150, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514361</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6545056</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1960-07-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1960-07-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Igenväxande fuktäng</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20942-2026 artfynd.xlsx
+++ b/artfynd/A 20942-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62155655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>